--- a/weeks/◆ 2026년 09월 1주 편성표 (0831 ~ 0906).xlsx
+++ b/weeks/◆ 2026년 09월 1주 편성표 (0831 ~ 0906).xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="39">
+  <fonts count="37">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
@@ -239,18 +239,6 @@
     <font>
       <name val="Arial"/>
       <sz val="9.0"/>
-      <color rgb="00333333"/>
-      <u val="none"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="9.0"/>
-      <color rgb="00333333"/>
-      <u val="none"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="9.0"/>
       <color rgb="001C970F"/>
       <u val="none"/>
     </font>
@@ -299,12 +287,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEEEEE"/>
+        <fgColor rgb="00DDFFC6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDFFC6"/>
+        <fgColor rgb="00EEEEEE"/>
       </patternFill>
     </fill>
   </fills>
@@ -372,7 +360,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="true" applyNumberFormat="true">
       <alignment wrapText="true"/>
@@ -485,22 +473,16 @@
     <xf numFmtId="49" fontId="32" fillId="9" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="33" fillId="9" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
+    <xf numFmtId="49" fontId="33" fillId="10" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
+      <alignment wrapText="true" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="34" fillId="10" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="34" fillId="8" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
-      <alignment wrapText="true" horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="35" fillId="10" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
-      <alignment wrapText="true" horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="9" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
-      <alignment wrapText="true" horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="37" fillId="6" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
+    <xf numFmtId="49" fontId="35" fillId="6" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="38" fillId="4" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
+    <xf numFmtId="49" fontId="36" fillId="4" borderId="6" xfId="0" applyAlignment="true" applyFill="true" applyBorder="true" applyNumberFormat="true" applyFont="true">
       <alignment wrapText="true" horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -517,48 +499,48 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="6.0"/>
-    <col min="2" max="2" customWidth="true" width="0.375"/>
-    <col min="3" max="3" customWidth="true" width="5.125"/>
-    <col min="4" max="4" customWidth="true" width="3.625"/>
-    <col min="5" max="5" customWidth="true" width="2.125"/>
-    <col min="6" max="6" customWidth="true" width="3.625"/>
-    <col min="7" max="7" customWidth="true" width="16.375"/>
-    <col min="8" max="8" customWidth="true" width="0.375"/>
-    <col min="9" max="9" customWidth="true" width="5.125"/>
-    <col min="10" max="10" customWidth="true" width="3.625"/>
-    <col min="11" max="11" customWidth="true" width="2.125"/>
-    <col min="12" max="12" customWidth="true" width="3.625"/>
-    <col min="13" max="13" customWidth="true" width="16.375"/>
-    <col min="14" max="14" customWidth="true" width="0.375"/>
-    <col min="15" max="15" customWidth="true" width="5.125"/>
-    <col min="16" max="16" customWidth="true" width="3.625"/>
-    <col min="17" max="17" customWidth="true" width="2.125"/>
-    <col min="18" max="18" customWidth="true" width="3.625"/>
-    <col min="19" max="19" customWidth="true" width="16.375"/>
-    <col min="20" max="20" customWidth="true" width="0.375"/>
-    <col min="21" max="21" customWidth="true" width="5.125"/>
-    <col min="22" max="22" customWidth="true" width="3.625"/>
-    <col min="23" max="23" customWidth="true" width="2.125"/>
-    <col min="24" max="24" customWidth="true" width="3.625"/>
-    <col min="25" max="25" customWidth="true" width="16.375"/>
-    <col min="26" max="26" customWidth="true" width="0.375"/>
-    <col min="27" max="27" customWidth="true" width="5.125"/>
-    <col min="28" max="28" customWidth="true" width="3.625"/>
-    <col min="29" max="29" customWidth="true" width="2.125"/>
-    <col min="30" max="30" customWidth="true" width="3.625"/>
-    <col min="31" max="31" customWidth="true" width="16.375"/>
-    <col min="32" max="32" customWidth="true" width="0.375"/>
-    <col min="33" max="33" customWidth="true" width="5.125"/>
-    <col min="34" max="34" customWidth="true" width="3.625"/>
-    <col min="35" max="35" customWidth="true" width="2.125"/>
-    <col min="36" max="36" customWidth="true" width="3.625"/>
-    <col min="37" max="37" customWidth="true" width="16.375"/>
-    <col min="38" max="38" customWidth="true" width="0.375"/>
-    <col min="39" max="39" customWidth="true" width="5.125"/>
-    <col min="40" max="40" customWidth="true" width="3.625"/>
-    <col min="41" max="41" customWidth="true" width="2.125"/>
-    <col min="42" max="42" customWidth="true" width="3.625"/>
-    <col min="43" max="43" customWidth="true" width="16.625"/>
+    <col min="2" max="2" customWidth="true" width="0.25"/>
+    <col min="3" max="3" customWidth="true" width="3.75"/>
+    <col min="4" max="4" customWidth="true" width="2.625"/>
+    <col min="5" max="5" customWidth="true" width="1.5"/>
+    <col min="6" max="6" customWidth="true" width="2.625"/>
+    <col min="7" max="7" customWidth="true" width="11.875"/>
+    <col min="8" max="8" customWidth="true" width="0.25"/>
+    <col min="9" max="9" customWidth="true" width="3.75"/>
+    <col min="10" max="10" customWidth="true" width="2.625"/>
+    <col min="11" max="11" customWidth="true" width="1.5"/>
+    <col min="12" max="12" customWidth="true" width="2.625"/>
+    <col min="13" max="13" customWidth="true" width="11.875"/>
+    <col min="14" max="14" customWidth="true" width="0.25"/>
+    <col min="15" max="15" customWidth="true" width="3.75"/>
+    <col min="16" max="16" customWidth="true" width="2.625"/>
+    <col min="17" max="17" customWidth="true" width="1.5"/>
+    <col min="18" max="18" customWidth="true" width="2.625"/>
+    <col min="19" max="19" customWidth="true" width="11.875"/>
+    <col min="20" max="20" customWidth="true" width="0.25"/>
+    <col min="21" max="21" customWidth="true" width="3.75"/>
+    <col min="22" max="22" customWidth="true" width="2.625"/>
+    <col min="23" max="23" customWidth="true" width="1.5"/>
+    <col min="24" max="24" customWidth="true" width="2.625"/>
+    <col min="25" max="25" customWidth="true" width="11.875"/>
+    <col min="26" max="26" customWidth="true" width="0.25"/>
+    <col min="27" max="27" customWidth="true" width="3.75"/>
+    <col min="28" max="28" customWidth="true" width="2.625"/>
+    <col min="29" max="29" customWidth="true" width="1.5"/>
+    <col min="30" max="30" customWidth="true" width="2.625"/>
+    <col min="31" max="31" customWidth="true" width="11.875"/>
+    <col min="32" max="32" customWidth="true" width="0.25"/>
+    <col min="33" max="33" customWidth="true" width="3.75"/>
+    <col min="34" max="34" customWidth="true" width="2.625"/>
+    <col min="35" max="35" customWidth="true" width="1.5"/>
+    <col min="36" max="36" customWidth="true" width="2.625"/>
+    <col min="37" max="37" customWidth="true" width="11.875"/>
+    <col min="38" max="38" customWidth="true" width="0.25"/>
+    <col min="39" max="39" customWidth="true" width="3.75"/>
+    <col min="40" max="40" customWidth="true" width="2.625"/>
+    <col min="41" max="41" customWidth="true" width="1.5"/>
+    <col min="42" max="42" customWidth="true" width="2.625"/>
+    <col min="43" max="43" customWidth="true" width="11.625"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="true" ht="24.75">
@@ -605,7 +587,7 @@
       <c r="AK1" s="4"/>
       <c r="AL1" s="4" t="inlineStr">
         <is>
-          <t>1차 확정안입니다.</t>
+          <t>확정 편성표입니다.</t>
         </is>
       </c>
       <c r="AM1" s="4"/>
@@ -901,12 +883,12 @@
       </c>
       <c r="F8" s="31" t="inlineStr">
         <is>
-          <t>'패션2Lab'</t>
+          <t>'패션3Lab'</t>
         </is>
       </c>
       <c r="G8" s="31" t="inlineStr">
         <is>
-          <t>NNF 신상품 런칭</t>
+          <t>테디크루 남녀 윈드재킷</t>
         </is>
       </c>
       <c r="H8" s="25"/>
@@ -928,12 +910,12 @@
       </c>
       <c r="L8" s="31" t="inlineStr">
         <is>
-          <t>'패션3Lab'</t>
+          <t>'패션2Lab'</t>
         </is>
       </c>
       <c r="M8" s="31" t="inlineStr">
         <is>
-          <t>테디크루 남녀 윈드재킷</t>
+          <t>NNF 신상품 런칭</t>
         </is>
       </c>
       <c r="N8" s="25"/>
@@ -1083,7 +1065,7 @@
       </c>
       <c r="D9" s="24" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E9" s="24" t="inlineStr">
@@ -1163,7 +1145,7 @@
       </c>
       <c r="V9" s="32" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>90</t>
         </is>
       </c>
       <c r="W9" s="24" t="inlineStr">
@@ -1271,12 +1253,12 @@
       <c r="B10" s="25"/>
       <c r="C10" s="29" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>75</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
@@ -1313,12 +1295,12 @@
       </c>
       <c r="L10" s="31" t="inlineStr">
         <is>
-          <t>'패션4Lab'</t>
+          <t>'건강식품2'</t>
         </is>
       </c>
       <c r="M10" s="31" t="inlineStr">
         <is>
-          <t>비버리힐즈폴로클럽 케이블 가디건 2종</t>
+          <t>여에스더 국민영양</t>
         </is>
       </c>
       <c r="N10" s="25"/>
@@ -1340,23 +1322,23 @@
       </c>
       <c r="R10" s="31" t="inlineStr">
         <is>
-          <t>'건강식품2'</t>
+          <t>'주방'</t>
         </is>
       </c>
       <c r="S10" s="31" t="inlineStr">
         <is>
-          <t>여에스더 국민영양</t>
+          <t>렌지프로</t>
         </is>
       </c>
       <c r="T10" s="25"/>
       <c r="U10" s="29" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="V10" s="32" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>30</t>
         </is>
       </c>
       <c r="W10" s="24" t="inlineStr">
@@ -1366,12 +1348,12 @@
       </c>
       <c r="X10" s="31" t="inlineStr">
         <is>
-          <t>'패션2Lab'</t>
+          <t>'잡화'</t>
         </is>
       </c>
       <c r="Y10" s="33" t="inlineStr">
         <is>
-          <t>로라파커 신상품 런칭</t>
+          <t>루이까또즈 울실크 스카프</t>
         </is>
       </c>
       <c r="Z10" s="25"/>
@@ -1393,12 +1375,12 @@
       </c>
       <c r="AD10" s="31" t="inlineStr">
         <is>
-          <t>'뷰티1'</t>
+          <t>'리빙'</t>
         </is>
       </c>
       <c r="AE10" s="31" t="inlineStr">
         <is>
-          <t>베지톨로지 앰플</t>
+          <t>욕실의여왕 탈취제</t>
         </is>
       </c>
       <c r="AF10" s="25"/>
@@ -1536,7 +1518,7 @@
       </c>
       <c r="S11" s="33" t="inlineStr">
         <is>
-          <t>프리마클라쎄 스니커즈 外</t>
+          <t>팀P-프리마클라쎄 스니커즈 外</t>
         </is>
       </c>
       <c r="T11" s="25"/>
@@ -1890,12 +1872,12 @@
       </c>
       <c r="L13" s="31" t="inlineStr">
         <is>
-          <t>'리빙'</t>
+          <t>'뷰티1'</t>
         </is>
       </c>
       <c r="M13" s="31" t="inlineStr">
         <is>
-          <t>욕실의여왕 탈취제</t>
+          <t>베지톨로지 앰플</t>
         </is>
       </c>
       <c r="N13" s="25"/>
@@ -1921,7 +1903,7 @@
       </c>
       <c r="S13" s="33" t="inlineStr">
         <is>
-          <t>유로컬렉션 26F/W 이태리 램스킨 코쿤 자켓</t>
+          <t>팀P-유로컬렉션 26F/W 이태리 램스킨 코쿤 자켓</t>
         </is>
       </c>
       <c r="T13" s="25"/>
@@ -2054,12 +2036,12 @@
       </c>
       <c r="F14" s="31" t="inlineStr">
         <is>
-          <t>'뷰티2'</t>
+          <t>'패션4Lab'</t>
         </is>
       </c>
       <c r="G14" s="31" t="inlineStr">
         <is>
-          <t>코이 크림</t>
+          <t>라우라 ss 의류+ 신발</t>
         </is>
       </c>
       <c r="H14" s="25"/>
@@ -2213,12 +2195,12 @@
       </c>
       <c r="AP14" s="31" t="inlineStr">
         <is>
-          <t>'주얼리'</t>
+          <t>'결제'</t>
         </is>
       </c>
       <c r="AQ14" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">디아넬로 24K </t>
+          <t>라클라우드 오가르 침대</t>
         </is>
       </c>
     </row>
@@ -2262,75 +2244,75 @@
       </c>
       <c r="J15" s="24" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K15" s="30" t="inlineStr">
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K15" s="24" t="inlineStr">
+        <is>
+          <t>대</t>
+        </is>
+      </c>
+      <c r="L15" s="31" t="inlineStr">
+        <is>
+          <t>'금융상품'</t>
+        </is>
+      </c>
+      <c r="M15" s="36" t="inlineStr">
+        <is>
+          <t>#금융상품</t>
+        </is>
+      </c>
+      <c r="N15" s="25"/>
+      <c r="O15" s="29" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="P15" s="24" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="Q15" s="30" t="inlineStr">
         <is>
           <t>중
 수</t>
         </is>
       </c>
-      <c r="L15" s="31" t="inlineStr">
-        <is>
-          <t>'패션4Lab'</t>
-        </is>
-      </c>
-      <c r="M15" s="31" t="inlineStr">
-        <is>
-          <t>라우라 ss 의류+ 신발</t>
-        </is>
-      </c>
-      <c r="N15" s="25"/>
-      <c r="O15" s="37" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="P15" s="24" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="Q15" s="24" t="inlineStr">
+      <c r="R15" s="31" t="inlineStr">
+        <is>
+          <t>'뷰티2'</t>
+        </is>
+      </c>
+      <c r="S15" s="31" t="inlineStr">
+        <is>
+          <t>코이 크림</t>
+        </is>
+      </c>
+      <c r="T15" s="25"/>
+      <c r="U15" s="29" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="W15" s="24" t="inlineStr">
         <is>
           <t>대</t>
         </is>
       </c>
-      <c r="R15" s="31" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="S15" s="38" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="T15" s="25"/>
-      <c r="U15" s="37" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="V15" s="24" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="W15" s="24" t="inlineStr">
-        <is>
-          <t>대</t>
-        </is>
-      </c>
       <c r="X15" s="31" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="Y15" s="38" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>'GA'</t>
+        </is>
+      </c>
+      <c r="Y15" s="36" t="inlineStr">
+        <is>
+          <t>#금융GA</t>
         </is>
       </c>
       <c r="Z15" s="25"/>
@@ -2344,20 +2326,19 @@
           <t>60</t>
         </is>
       </c>
-      <c r="AC15" s="30" t="inlineStr">
-        <is>
-          <t>중
-수</t>
+      <c r="AC15" s="24" t="inlineStr">
+        <is>
+          <t>중</t>
         </is>
       </c>
       <c r="AD15" s="31" t="inlineStr">
         <is>
-          <t>'주방'</t>
+          <t>P.D.Lab</t>
         </is>
       </c>
       <c r="AE15" s="31" t="inlineStr">
         <is>
-          <t>헤르젠 쌀냉장고</t>
+          <t>알레보 316 한수저</t>
         </is>
       </c>
       <c r="AF15" s="25"/>
@@ -2449,27 +2430,28 @@
       <c r="H16" s="25"/>
       <c r="I16" s="29" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="J16" s="24" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K16" s="24" t="inlineStr">
-        <is>
-          <t>대</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K16" s="30" t="inlineStr">
+        <is>
+          <t>대
+수</t>
         </is>
       </c>
       <c r="L16" s="31" t="inlineStr">
         <is>
-          <t>'금융상품'</t>
-        </is>
-      </c>
-      <c r="M16" s="36" t="inlineStr">
-        <is>
-          <t>#금융상품</t>
+          <t>'가전'</t>
+        </is>
+      </c>
+      <c r="M16" s="31" t="inlineStr">
+        <is>
+          <t>LG 건조기</t>
         </is>
       </c>
       <c r="N16" s="25"/>
@@ -2714,7 +2696,7 @@
       </c>
       <c r="Y17" s="35" t="inlineStr">
         <is>
-          <t>LG 건조기</t>
+          <t>LG공기청정기</t>
         </is>
       </c>
       <c r="Z17" s="25"/>
@@ -2754,19 +2736,20 @@
           <t>70</t>
         </is>
       </c>
-      <c r="AI17" s="24" t="inlineStr">
-        <is>
-          <t>대</t>
+      <c r="AI17" s="30" t="inlineStr">
+        <is>
+          <t>중
+수</t>
         </is>
       </c>
       <c r="AJ17" s="31" t="inlineStr">
         <is>
-          <t>'금융상품'</t>
-        </is>
-      </c>
-      <c r="AK17" s="39" t="inlineStr">
-        <is>
-          <t>#금융상품</t>
+          <t>'주얼리'</t>
+        </is>
+      </c>
+      <c r="AK17" s="31" t="inlineStr">
+        <is>
+          <t>한민 18K</t>
         </is>
       </c>
       <c r="AL17" s="25"/>
@@ -2846,7 +2829,7 @@
 수</t>
         </is>
       </c>
-      <c r="L18" s="40" t="inlineStr">
+      <c r="L18" s="37" t="inlineStr">
         <is>
           <t>'일반식품2'</t>
         </is>
@@ -2899,7 +2882,7 @@
 수</t>
         </is>
       </c>
-      <c r="X18" s="40" t="inlineStr">
+      <c r="X18" s="37" t="inlineStr">
         <is>
           <t>'일반식품2'</t>
         </is>
@@ -2947,20 +2930,19 @@
           <t>60</t>
         </is>
       </c>
-      <c r="AI18" s="30" t="inlineStr">
-        <is>
-          <t>중
-수</t>
+      <c r="AI18" s="24" t="inlineStr">
+        <is>
+          <t>대</t>
         </is>
       </c>
       <c r="AJ18" s="31" t="inlineStr">
         <is>
-          <t>'주방'</t>
-        </is>
-      </c>
-      <c r="AK18" s="31" t="inlineStr">
-        <is>
-          <t>렌지프로</t>
+          <t>'금융상품'</t>
+        </is>
+      </c>
+      <c r="AK18" s="36" t="inlineStr">
+        <is>
+          <t>#금융상품</t>
         </is>
       </c>
       <c r="AL18" s="25"/>
@@ -3130,7 +3112,7 @@
         </is>
       </c>
       <c r="AF19" s="25"/>
-      <c r="AG19" s="37" t="inlineStr">
+      <c r="AG19" s="38" t="inlineStr">
         <is>
           <t>17:05</t>
         </is>
@@ -3150,7 +3132,7 @@
           <t>옴부즈맨</t>
         </is>
       </c>
-      <c r="AK19" s="41" t="inlineStr">
+      <c r="AK19" s="39" t="inlineStr">
         <is>
           <t>포커스현대홈쇼핑-옴부즈맨</t>
         </is>
@@ -3177,7 +3159,7 @@
           <t>'해외여행'</t>
         </is>
       </c>
-      <c r="AQ19" s="42" t="inlineStr">
+      <c r="AQ19" s="40" t="inlineStr">
         <is>
           <t>참좋은여행 유럽</t>
         </is>
@@ -3210,7 +3192,7 @@
           <t>'일반식품1'</t>
         </is>
       </c>
-      <c r="G20" s="42" t="inlineStr">
+      <c r="G20" s="40" t="inlineStr">
         <is>
           <t>제주생고사리</t>
         </is>
@@ -3403,7 +3385,7 @@
           <t>'일반식품1'</t>
         </is>
       </c>
-      <c r="G21" s="42" t="inlineStr">
+      <c r="G21" s="40" t="inlineStr">
         <is>
           <t>박정수순살조기(직전2/2)</t>
         </is>
@@ -3664,46 +3646,46 @@
           <t>60</t>
         </is>
       </c>
-      <c r="W22" s="30" t="inlineStr">
+      <c r="W22" s="24" t="inlineStr">
+        <is>
+          <t>대</t>
+        </is>
+      </c>
+      <c r="X22" s="31" t="inlineStr">
+        <is>
+          <t>'금융상품'</t>
+        </is>
+      </c>
+      <c r="Y22" s="36" t="inlineStr">
+        <is>
+          <t>#금융상품</t>
+        </is>
+      </c>
+      <c r="Z22" s="25"/>
+      <c r="AA22" s="29" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AB22" s="24" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AC22" s="30" t="inlineStr">
         <is>
           <t>중
 수</t>
         </is>
       </c>
-      <c r="X22" s="31" t="inlineStr">
+      <c r="AD22" s="31" t="inlineStr">
         <is>
           <t>'뷰티1'</t>
         </is>
       </c>
-      <c r="Y22" s="31" t="inlineStr">
+      <c r="AE22" s="31" t="inlineStr">
         <is>
           <t>리더스 아이크림</t>
-        </is>
-      </c>
-      <c r="Z22" s="25"/>
-      <c r="AA22" s="29" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="AB22" s="24" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="AC22" s="24" t="inlineStr">
-        <is>
-          <t>대</t>
-        </is>
-      </c>
-      <c r="AD22" s="31" t="inlineStr">
-        <is>
-          <t>'GA'</t>
-        </is>
-      </c>
-      <c r="AE22" s="36" t="inlineStr">
-        <is>
-          <t>#금융GA</t>
         </is>
       </c>
       <c r="AF22" s="25"/>
@@ -3788,7 +3770,7 @@
           <t>'일반식품1'</t>
         </is>
       </c>
-      <c r="G23" s="42" t="inlineStr">
+      <c r="G23" s="40" t="inlineStr">
         <is>
           <t>영암 무화과</t>
         </is>
@@ -3814,7 +3796,7 @@
           <t>'리빙'</t>
         </is>
       </c>
-      <c r="M23" s="42" t="inlineStr">
+      <c r="M23" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">까사무띠 NEW 보그 커트러리 4인조 풀세트 </t>
         </is>
@@ -3979,7 +3961,7 @@
           <t>'리빙'</t>
         </is>
       </c>
-      <c r="G24" s="42" t="inlineStr">
+      <c r="G24" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">에비스 칫솔 </t>
         </is>
@@ -4005,7 +3987,7 @@
           <t>'일반식품1'</t>
         </is>
       </c>
-      <c r="M24" s="42" t="inlineStr">
+      <c r="M24" s="40" t="inlineStr">
         <is>
           <t>거창 홍로사과</t>
         </is>
@@ -4073,10 +4055,9 @@
           <t>55</t>
         </is>
       </c>
-      <c r="AC24" s="30" t="inlineStr">
-        <is>
-          <t>중
-수</t>
+      <c r="AC24" s="24" t="inlineStr">
+        <is>
+          <t>수</t>
         </is>
       </c>
       <c r="AD24" s="31" t="inlineStr">
@@ -4086,7 +4067,7 @@
       </c>
       <c r="AE24" s="31" t="inlineStr">
         <is>
-          <t>캐롤프랑크 클렌저</t>
+          <t>캐롤프랑크 비비크림</t>
         </is>
       </c>
       <c r="AF24" s="25"/>
@@ -4170,7 +4151,7 @@
           <t>'액티브라이프'</t>
         </is>
       </c>
-      <c r="G25" s="42" t="inlineStr">
+      <c r="G25" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">곡물도감 </t>
         </is>
@@ -4196,7 +4177,7 @@
           <t>'일반식품1'</t>
         </is>
       </c>
-      <c r="M25" s="42" t="inlineStr">
+      <c r="M25" s="40" t="inlineStr">
         <is>
           <t>베스트넛츠 견과</t>
         </is>
@@ -4220,12 +4201,12 @@
       </c>
       <c r="R25" s="31" t="inlineStr">
         <is>
-          <t>'잡화'</t>
+          <t>'주얼리'</t>
         </is>
       </c>
       <c r="S25" s="31" t="inlineStr">
         <is>
-          <t>베라왕 로퍼</t>
+          <t xml:space="preserve">디아넬로 24K </t>
         </is>
       </c>
       <c r="T25" s="25"/>
@@ -4381,18 +4362,18 @@
       </c>
       <c r="K26" s="30" t="inlineStr">
         <is>
-          <t>대
+          <t>중
 수</t>
         </is>
       </c>
       <c r="L26" s="31" t="inlineStr">
         <is>
-          <t>'리빙'</t>
+          <t>'잡화'</t>
         </is>
       </c>
       <c r="M26" s="31" t="inlineStr">
         <is>
-          <t>오토드 진공스팀다리미</t>
+          <t>베라왕 로퍼</t>
         </is>
       </c>
       <c r="N26" s="25"/>
@@ -4494,7 +4475,7 @@
           <t>'금융상품'</t>
         </is>
       </c>
-      <c r="AK26" s="39" t="inlineStr">
+      <c r="AK26" s="36" t="inlineStr">
         <is>
           <t>#금융상품</t>
         </is>
@@ -4606,19 +4587,20 @@
           <t>65</t>
         </is>
       </c>
-      <c r="W27" s="24" t="inlineStr">
-        <is>
-          <t>대</t>
+      <c r="W27" s="30" t="inlineStr">
+        <is>
+          <t>대
+수</t>
         </is>
       </c>
       <c r="X27" s="31" t="inlineStr">
         <is>
-          <t>'금융상품'</t>
-        </is>
-      </c>
-      <c r="Y27" s="36" t="inlineStr">
-        <is>
-          <t>#금융상품</t>
+          <t>'뷰티2'</t>
+        </is>
+      </c>
+      <c r="Y27" s="31" t="inlineStr">
+        <is>
+          <t>에이지 팩트</t>
         </is>
       </c>
       <c r="Z27" s="25"/>
@@ -4648,7 +4630,7 @@
         </is>
       </c>
       <c r="AF27" s="25"/>
-      <c r="AG27" s="37" t="inlineStr">
+      <c r="AG27" s="29" t="inlineStr">
         <is>
           <t>00:30</t>
         </is>
@@ -4660,17 +4642,17 @@
       </c>
       <c r="AI27" s="24" t="inlineStr">
         <is>
-          <t>대</t>
+          <t>중</t>
         </is>
       </c>
       <c r="AJ27" s="31" t="inlineStr">
         <is>
-          <t>Hit &amp; Best</t>
-        </is>
-      </c>
-      <c r="AK27" s="41" t="inlineStr">
-        <is>
-          <t>Hit &amp; Best</t>
+          <t>'리빙'</t>
+        </is>
+      </c>
+      <c r="AK27" s="31" t="inlineStr">
+        <is>
+          <t>전설의패치 570매</t>
         </is>
       </c>
       <c r="AL27" s="25"/>
@@ -4880,7 +4862,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="F29" s="40" t="inlineStr">
+      <c r="F29" s="37" t="inlineStr">
         <is>
           <t>'일반식품1'</t>
         </is>
@@ -4891,7 +4873,7 @@
         </is>
       </c>
       <c r="H29" s="25"/>
-      <c r="I29" s="43" t="inlineStr">
+      <c r="I29" s="41" t="inlineStr">
         <is>
           <t>01:00</t>
         </is>
